--- a/week-04/Top 5 hero products.xlsx
+++ b/week-04/Top 5 hero products.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onurkaraer\Documents\DataAnalytics\week-04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3ACFB39-60AD-440B-9887-6D731F1F0AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3E55C3-444E-46C4-9BEF-60963841C038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B2EE8552-B390-4D25-8FB0-AA18FFA06691}"/>
   </bookViews>
   <sheets>
     <sheet name="data-1777485697858" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -916,6 +916,8 @@
   <cols>
     <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
